--- a/Data/Home/BedroomOne.Temperature.xlsx
+++ b/Data/Home/BedroomOne.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709236512</v>
+        <v>1711833634</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709263618</v>
+        <v>1711864651</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272162</v>
+        <v>1711873036</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709280563</v>
+        <v>1711897047</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709286255</v>
+        <v>1711897434</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709292300</v>
+        <v>1711938430</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709231620</v>
+        <v>1711948850</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709245363</v>
+        <v>1711961615</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,15 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709256246</v>
+        <v>1711976072</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +774,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709261823</v>
+        <v>1711977694</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +803,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +826,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709271777</v>
+        <v>1711978079</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +836,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +859,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709280285</v>
+        <v>1711989341</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +873,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +892,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709318876</v>
+        <v>1712000807</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +906,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +925,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709334169</v>
+        <v>1712025352</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +939,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +958,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709347450</v>
+        <v>1712029485</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +972,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709357914</v>
+        <v>1712041306</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1005,11 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709365180</v>
+        <v>1712056440</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1042,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1061,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709370354</v>
+        <v>1712058540</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1075,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1094,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709435155</v>
+        <v>1712092751</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1104,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1127,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709440589</v>
+        <v>1712110432</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1137,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1160,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709455134</v>
+        <v>1712115120</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1174,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709461294</v>
+        <v>1712126985</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1203,15 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709516563</v>
+        <v>1712140735</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1244,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709523117</v>
+        <v>1712147526</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1273,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709541293</v>
+        <v>1712147922</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1306,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709547206</v>
+        <v>1712150285</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1343,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1362,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709605785</v>
+        <v>1712172497</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1372,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709633038</v>
+        <v>1712195215</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1409,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1428,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709666216</v>
+        <v>1712200892</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1438,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1461,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709679135</v>
+        <v>1712212780</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1471,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1498,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709689754</v>
+        <v>1712224854</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1512,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1531,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709718370</v>
+        <v>1712225118</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1545,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1564,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709722991</v>
+        <v>1712229364</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1574,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1597,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709767715</v>
+        <v>1712239601</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1630,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709773464</v>
+        <v>1712259829</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1640,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1663,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709783252</v>
+        <v>1712287616</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1673,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1696,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709794729</v>
+        <v>1712296113</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1710,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1729,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709799714</v>
+        <v>1712306448</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1739,15 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709835070</v>
+        <v>1712315128</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1776,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709848984</v>
+        <v>1712315394</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1813,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1832,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709859115</v>
+        <v>1712351414</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1842,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1865,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709866364</v>
+        <v>1712380865</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1875,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1898,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709882198</v>
+        <v>1712389345</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1912,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1931,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709887224</v>
+        <v>1712413547</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1945,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1964,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709953002</v>
+        <v>1712432791</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1974,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1997,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709959640</v>
+        <v>1712460840</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2007,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2030,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709969012</v>
+        <v>1712469209</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2044,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2063,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709978061</v>
+        <v>1712479785</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2073,15 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2100,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710005092</v>
+        <v>1712494161</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2110,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2133,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710021520</v>
+        <v>1712502642</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2147,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2166,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710030457</v>
+        <v>1712524467</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2176,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2199,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710034709</v>
+        <v>1712547483</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2209,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2232,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710039292</v>
+        <v>1712553950</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2246,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2265,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710042258</v>
+        <v>1712567913</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2275,11 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2298,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710051743</v>
+        <v>1712568384</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2308,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710056870</v>
+        <v>1712569704</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2345,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2364,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710061178</v>
+        <v>1712572250</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2374,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2397,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710089506</v>
+        <v>1712584651</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2411,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2430,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710108733</v>
+        <v>1712604735</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2444,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2463,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710114084</v>
+        <v>1712634136</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2477,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2496,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710120390</v>
+        <v>1712642603</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2510,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2529,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710127962</v>
+        <v>1712653177</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2566,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710144039</v>
+        <v>1712666640</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2580,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2599,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710150766</v>
+        <v>1712666887</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2613,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2632,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710197404</v>
+        <v>1712667277</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2646,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2665,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710203927</v>
+        <v>1712682383</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2679,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2698,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710216133</v>
+        <v>1712691529</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2708,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2731,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710238421</v>
+        <v>1712715032</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2745,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2764,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710301518</v>
+        <v>1712720129</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2778,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2797,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710321490</v>
+        <v>1712732538</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2807,15 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2834,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710329959</v>
+        <v>1712747616</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2844,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2867,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710349001</v>
+        <v>1712756439</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2881,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2900,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710352767</v>
+        <v>1712762100</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2914,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2933,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710367285</v>
+        <v>1712765475</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2947,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2966,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710381198</v>
+        <v>1712778482</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2976,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2999,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710406819</v>
+        <v>1712806534</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3013,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3032,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710411045</v>
+        <v>1712815140</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3042,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3065,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710452386</v>
+        <v>1712823702</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3075,15 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3102,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710469455</v>
+        <v>1712830653</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3116,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3135,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710476332</v>
+        <v>1712830893</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3145,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3168,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710490714</v>
+        <v>1712868770</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3178,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3201,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710496381</v>
+        <v>1712892717</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3215,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3234,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710533864</v>
+        <v>1712901252</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3244,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3267,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710541568</v>
+        <v>1712910701</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3277,15 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3304,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710551689</v>
+        <v>1712921828</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3318,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3337,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710569456</v>
+        <v>1712922091</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3347,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3370,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710572580</v>
+        <v>1712951761</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3380,11 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3403,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710576535</v>
+        <v>1712982728</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3417,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3436,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710619457</v>
+        <v>1712991886</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3446,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3469,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710628223</v>
+        <v>1713017789</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3483,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3502,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710635555</v>
+        <v>1713037014</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3512,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3535,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710641146</v>
+        <v>1713063403</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3545,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3568,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710654094</v>
+        <v>1713071913</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3582,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3601,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710662361</v>
+        <v>1713082593</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3611,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3638,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710698876</v>
+        <v>1713098558</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3648,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3671,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710716385</v>
+        <v>1713108070</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3685,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3704,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710727449</v>
+        <v>1713127744</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3714,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3737,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710733323</v>
+        <v>1713157472</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3747,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3770,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710753239</v>
+        <v>1713164253</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3784,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3803,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710757380</v>
+        <v>1713174533</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3817,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3836,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710787332</v>
+        <v>1713202827</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3850,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3869,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710800197</v>
+        <v>1713214989</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3883,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3902,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710809845</v>
+        <v>1713238879</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3916,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3935,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710814736</v>
+        <v>1713247404</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3949,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3972,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710829237</v>
+        <v>1713265484</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3986,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4005,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710837374</v>
+        <v>1713265759</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4019,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4038,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710871866</v>
+        <v>1713300302</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4052,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4071,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710888743</v>
+        <v>1713321319</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4085,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4104,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710897502</v>
+        <v>1713325456</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4118,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4137,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710926365</v>
+        <v>1713338245</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4147,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4174,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710931210</v>
+        <v>1713352052</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4184,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4207,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710954050</v>
+        <v>1713353851</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4221,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4240,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710959699</v>
+        <v>1713385549</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4254,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4273,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710972737</v>
+        <v>1713410182</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4287,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4306,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710986578</v>
+        <v>1713417795</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4320,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4339,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711014524</v>
+        <v>1713442464</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4353,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4372,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711020575</v>
+        <v>1713445424</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4386,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4405,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711059633</v>
+        <v>1713448747</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4419,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4438,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711068160</v>
+        <v>1713470283</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4273,10 +4448,11 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4471,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711093643</v>
+        <v>1713493637</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4485,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4504,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711098361</v>
+        <v>1713497370</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4514,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4537,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711148931</v>
+        <v>1713509134</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4547,15 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4574,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711159245</v>
+        <v>1713524550</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4588,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4607,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711164955</v>
+        <v>1713527945</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4617,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4640,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711176576</v>
+        <v>1713554766</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4650,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4673,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711183995</v>
+        <v>1713584402</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4687,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4706,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711218747</v>
+        <v>1713591261</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4716,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4739,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711233924</v>
+        <v>1713598251</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4749,15 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4776,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711247031</v>
+        <v>1713614148</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4790,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4809,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711256701</v>
+        <v>1713623195</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4819,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4842,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711271901</v>
+        <v>1713636249</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4852,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4875,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711278266</v>
+        <v>1713664659</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4889,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4908,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711307287</v>
+        <v>1713668937</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4918,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4941,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711319538</v>
+        <v>1713680278</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4951,15 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4978,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711332250</v>
+        <v>1713694222</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4992,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5011,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711341045</v>
+        <v>1713701908</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5021,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5044,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711356375</v>
+        <v>1713722237</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +5054,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5077,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711362045</v>
+        <v>1713750555</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5091,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5110,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711421298</v>
+        <v>1713755481</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5124,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5143,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711425382</v>
+        <v>1713767767</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5157,11 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5180,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711443647</v>
+        <v>1713778677</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5194,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5213,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711452852</v>
+        <v>1713778964</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5227,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5246,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711461789</v>
+        <v>1713782912</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5256,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5279,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711480681</v>
+        <v>1713794065</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5293,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5312,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711512691</v>
+        <v>1713814517</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5322,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5345,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711518695</v>
+        <v>1713843261</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5359,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5378,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711525003</v>
+        <v>1713850839</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5392,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5411,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711534359</v>
+        <v>1713856019</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5421,15 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Comfortable</t>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5448,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711547039</v>
+        <v>1713872871</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5458,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Cold</t>
+          <t>BedroomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5481,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711554976</v>
+        <v>1713873136</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5495,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5514,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711561652</v>
+        <v>1713873549</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5528,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5547,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711569985</v>
+        <v>1713881691</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5561,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5580,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711594200</v>
+        <v>1713905594</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5590,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>BedroomOne.Temperature.state: Warm</t>
+          <t>BedroomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5613,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711603166</v>
+        <v>1713935113</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5627,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5646,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711611105</v>
+        <v>1713943750</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5660,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5679,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711618537</v>
+        <v>1713950863</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5693,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5712,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711633568</v>
+        <v>1713951267</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5726,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5745,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711639730</v>
+        <v>1713956143</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5759,877 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1713995914</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1714015473</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1714022263</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1714041112</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1714075886</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1714102755</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1714111232</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1714121429</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1714135908</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1714136158</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1714136554</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1714146553</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1714160012</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1714186965</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1714195345</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1714207994</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1714223181</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1714231981</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1714232978</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1714237246</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1714247478</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1714276032</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1714284426</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1714294196</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1714310223</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1714320206</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>BedroomOne.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
